--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/146.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/146.xlsx
@@ -426,13 +426,13 @@
         <v>1.595338546657428</v>
       </c>
       <c r="E2">
-        <v>-4.249567370245543</v>
+        <v>-6.55818341935589</v>
       </c>
       <c r="F2">
-        <v>-3.9781036154921</v>
+        <v>-3.938525220959353</v>
       </c>
       <c r="G2">
-        <v>-0.9692726052927698</v>
+        <v>-2.073177325908286</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>1.819443572824273</v>
       </c>
       <c r="E3">
-        <v>-6.134109942433592</v>
+        <v>-8.082254932059373</v>
       </c>
       <c r="F3">
-        <v>-4.300644329642329</v>
+        <v>-3.504281769328391</v>
       </c>
       <c r="G3">
-        <v>-0.7923140145821072</v>
+        <v>-2.00330164121089</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>2.039835846610615</v>
       </c>
       <c r="E4">
-        <v>-6.402331457907907</v>
+        <v>-6.9322580147595</v>
       </c>
       <c r="F4">
-        <v>-4.548035822546082</v>
+        <v>-4.064225543173698</v>
       </c>
       <c r="G4">
-        <v>-0.6461368762955878</v>
+        <v>-1.473799745477699</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>2.24122105685125</v>
       </c>
       <c r="E5">
-        <v>-6.239220352625629</v>
+        <v>-7.236358629796587</v>
       </c>
       <c r="F5">
-        <v>-4.623824860982396</v>
+        <v>-3.864179730464964</v>
       </c>
       <c r="G5">
-        <v>-0.8228537971818838</v>
+        <v>-2.057786599696215</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>2.452773308837165</v>
       </c>
       <c r="E6">
-        <v>-7.110480637805375</v>
+        <v>-9.181922389237995</v>
       </c>
       <c r="F6">
-        <v>-4.35430266161629</v>
+        <v>-3.347718186233963</v>
       </c>
       <c r="G6">
-        <v>-0.9903971963788594</v>
+        <v>-3.445934760313556</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>2.68644529866625</v>
       </c>
       <c r="E7">
-        <v>-7.002064441587739</v>
+        <v>-8.964315627747412</v>
       </c>
       <c r="F7">
-        <v>-4.552933433089579</v>
+        <v>-3.410973776055488</v>
       </c>
       <c r="G7">
-        <v>-1.206807558281017</v>
+        <v>-2.091958050752572</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>2.964295736001277</v>
       </c>
       <c r="E8">
-        <v>-7.693947342849654</v>
+        <v>-9.401757159940352</v>
       </c>
       <c r="F8">
-        <v>-4.921457048494593</v>
+        <v>-3.838424713015129</v>
       </c>
       <c r="G8">
-        <v>-0.7735200475556646</v>
+        <v>-2.349306618793357</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.306028571501265</v>
       </c>
       <c r="E9">
-        <v>-9.638415211581206</v>
+        <v>-10.42795012634453</v>
       </c>
       <c r="F9">
-        <v>-4.956931269147479</v>
+        <v>-4.055579300728356</v>
       </c>
       <c r="G9">
-        <v>-0.26329545849765</v>
+        <v>-2.512731699339479</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>3.719555930090687</v>
       </c>
       <c r="E10">
-        <v>-9.7762076186866</v>
+        <v>-11.99920380973392</v>
       </c>
       <c r="F10">
-        <v>-4.679458866085867</v>
+        <v>-4.004303654304173</v>
       </c>
       <c r="G10">
-        <v>0.6483029822871427</v>
+        <v>-1.088114569061527</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.209608002690019</v>
       </c>
       <c r="E11">
-        <v>-10.99703439794044</v>
+        <v>-13.81583738570295</v>
       </c>
       <c r="F11">
-        <v>-4.422821698047779</v>
+        <v>-4.15547471875653</v>
       </c>
       <c r="G11">
-        <v>0.565075867429865</v>
+        <v>-1.516383292749344</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.773634075597752</v>
       </c>
       <c r="E12">
-        <v>-11.40861381507558</v>
+        <v>-14.13721865755331</v>
       </c>
       <c r="F12">
-        <v>-4.577735851431276</v>
+        <v>-3.797563516690876</v>
       </c>
       <c r="G12">
-        <v>0.7624108659347419</v>
+        <v>-1.500495984706382</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.388350431900125</v>
       </c>
       <c r="E13">
-        <v>-12.85441971150449</v>
+        <v>-15.21701969926028</v>
       </c>
       <c r="F13">
-        <v>-4.297491171164689</v>
+        <v>-3.829563086565288</v>
       </c>
       <c r="G13">
-        <v>1.371071216057446</v>
+        <v>-1.466003410732715</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>6.031999016198503</v>
       </c>
       <c r="E14">
-        <v>-13.79882390885613</v>
+        <v>-15.6120566008454</v>
       </c>
       <c r="F14">
-        <v>-4.476524373787372</v>
+        <v>-3.559749485310743</v>
       </c>
       <c r="G14">
-        <v>1.148215221990327</v>
+        <v>0.293346289566486</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.675526426174645</v>
       </c>
       <c r="E15">
-        <v>-14.74037516758294</v>
+        <v>-16.26354098548488</v>
       </c>
       <c r="F15">
-        <v>-4.137392756466999</v>
+        <v>-3.123597668051676</v>
       </c>
       <c r="G15">
-        <v>2.018829108998943</v>
+        <v>0.1508802728294897</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>7.278903448630692</v>
       </c>
       <c r="E16">
-        <v>-15.83613455169294</v>
+        <v>-17.19704967437407</v>
       </c>
       <c r="F16">
-        <v>-3.619504293206188</v>
+        <v>-2.390881081067419</v>
       </c>
       <c r="G16">
-        <v>2.453973835771826</v>
+        <v>0.3871539079672743</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.813932480220681</v>
       </c>
       <c r="E17">
-        <v>-17.13217928421419</v>
+        <v>-17.89784008400907</v>
       </c>
       <c r="F17">
-        <v>-3.711854144400251</v>
+        <v>-2.917685016779197</v>
       </c>
       <c r="G17">
-        <v>2.595185155749439</v>
+        <v>0.6883539622212455</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>8.250190371105679</v>
       </c>
       <c r="E18">
-        <v>-18.21112444433371</v>
+        <v>-19.42818353321318</v>
       </c>
       <c r="F18">
-        <v>-3.366081256323483</v>
+        <v>-2.590369429293919</v>
       </c>
       <c r="G18">
-        <v>3.5293648276576</v>
+        <v>2.549718123313088</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.556649884278587</v>
       </c>
       <c r="E19">
-        <v>-17.64403722977518</v>
+        <v>-19.4464423404121</v>
       </c>
       <c r="F19">
-        <v>-3.591269192292776</v>
+        <v>-2.645066672348408</v>
       </c>
       <c r="G19">
-        <v>3.506210872155938</v>
+        <v>1.312812235657352</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.716774493632016</v>
       </c>
       <c r="E20">
-        <v>-20.36454063225318</v>
+        <v>-22.20672385857349</v>
       </c>
       <c r="F20">
-        <v>-2.582571261366295</v>
+        <v>-2.121693043649473</v>
       </c>
       <c r="G20">
-        <v>4.028734137892345</v>
+        <v>2.129639689289428</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>8.713592082820504</v>
       </c>
       <c r="E21">
-        <v>-21.29412766265173</v>
+        <v>-22.54764549576694</v>
       </c>
       <c r="F21">
-        <v>-2.364616902165772</v>
+        <v>-1.874962747965415</v>
       </c>
       <c r="G21">
-        <v>3.339614288983193</v>
+        <v>1.801994997267759</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.537453754397749</v>
       </c>
       <c r="E22">
-        <v>-20.33109785170654</v>
+        <v>-22.12756613291941</v>
       </c>
       <c r="F22">
-        <v>-1.86824466747212</v>
+        <v>-1.485880254219125</v>
       </c>
       <c r="G22">
-        <v>4.177255142420668</v>
+        <v>1.425238362171001</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.19083124143733</v>
       </c>
       <c r="E23">
-        <v>-21.61285072025958</v>
+        <v>-25.05873414623424</v>
       </c>
       <c r="F23">
-        <v>-2.39138786696036</v>
+        <v>-0.9131567654891798</v>
       </c>
       <c r="G23">
-        <v>3.464024590349005</v>
+        <v>2.272383791851723</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.677977621849452</v>
       </c>
       <c r="E24">
-        <v>-22.10246027302088</v>
+        <v>-22.89233482333478</v>
       </c>
       <c r="F24">
-        <v>-1.852326047463081</v>
+        <v>-0.8793098026644079</v>
       </c>
       <c r="G24">
-        <v>3.700549826947774</v>
+        <v>3.528497464726311</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.015215750378287</v>
       </c>
       <c r="E25">
-        <v>-22.16851712337077</v>
+        <v>-23.82064935253716</v>
       </c>
       <c r="F25">
-        <v>-1.096035997927508</v>
+        <v>-0.7340815946597374</v>
       </c>
       <c r="G25">
-        <v>3.131294900379015</v>
+        <v>1.333317754727597</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>6.226157651994913</v>
       </c>
       <c r="E26">
-        <v>-22.08863937034947</v>
+        <v>-23.84476347662801</v>
       </c>
       <c r="F26">
-        <v>-1.584674996636068</v>
+        <v>-0.3316476681933349</v>
       </c>
       <c r="G26">
-        <v>2.802580902148161</v>
+        <v>1.253013851581496</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.334867609993942</v>
       </c>
       <c r="E27">
-        <v>-23.05459457550361</v>
+        <v>-24.1658685115639</v>
       </c>
       <c r="F27">
-        <v>-1.023316973408275</v>
+        <v>0.09576446797137858</v>
       </c>
       <c r="G27">
-        <v>2.902009826874631</v>
+        <v>2.172776097666131</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.377062981898805</v>
       </c>
       <c r="E28">
-        <v>-22.91799768553625</v>
+        <v>-23.94676282517677</v>
       </c>
       <c r="F28">
-        <v>-1.079734121086932</v>
+        <v>-0.1086840471822769</v>
       </c>
       <c r="G28">
-        <v>2.46013476102041</v>
+        <v>1.372203422631877</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.390333339052427</v>
       </c>
       <c r="E29">
-        <v>-22.02569358164286</v>
+        <v>-24.71710606709559</v>
       </c>
       <c r="F29">
-        <v>-0.8752222576966587</v>
+        <v>-0.2705403754461039</v>
       </c>
       <c r="G29">
-        <v>1.182035755219522</v>
+        <v>1.930162767820643</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.409794931854769</v>
       </c>
       <c r="E30">
-        <v>-21.86869591627093</v>
+        <v>-24.81424183456011</v>
       </c>
       <c r="F30">
-        <v>-1.163866914138737</v>
+        <v>-0.7400743378437603</v>
       </c>
       <c r="G30">
-        <v>0.927189959606426</v>
+        <v>0.2642366626396744</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.481358832692931</v>
       </c>
       <c r="E31">
-        <v>-22.31905718480776</v>
+        <v>-23.89699942430649</v>
       </c>
       <c r="F31">
-        <v>-0.7936170592858949</v>
+        <v>-0.3933638958650525</v>
       </c>
       <c r="G31">
-        <v>1.538343150520201</v>
+        <v>0.734102391028434</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.6473104964286779</v>
       </c>
       <c r="E32">
-        <v>-22.53424574117824</v>
+        <v>-23.18868269087073</v>
       </c>
       <c r="F32">
-        <v>-0.9291799100886384</v>
+        <v>-0.1765410945411109</v>
       </c>
       <c r="G32">
-        <v>1.265590614085187</v>
+        <v>0.1459773548858291</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.05975414709188866</v>
       </c>
       <c r="E33">
-        <v>-20.48927744879446</v>
+        <v>-23.14512329939095</v>
       </c>
       <c r="F33">
-        <v>-1.382777831712185</v>
+        <v>-0.9211877381863732</v>
       </c>
       <c r="G33">
-        <v>0.6428074766919525</v>
+        <v>0.6591549505648736</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.6022194139755523</v>
       </c>
       <c r="E34">
-        <v>-20.31787923607815</v>
+        <v>-22.27144480909111</v>
       </c>
       <c r="F34">
-        <v>-1.288403212505233</v>
+        <v>-0.8524343132794006</v>
       </c>
       <c r="G34">
-        <v>1.000376189843094</v>
+        <v>-0.5257422666689126</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9550392912634974</v>
       </c>
       <c r="E35">
-        <v>-20.26225146136792</v>
+        <v>-22.77702176120346</v>
       </c>
       <c r="F35">
-        <v>-1.45189867639154</v>
+        <v>-0.6910776442318948</v>
       </c>
       <c r="G35">
-        <v>1.434368846768311</v>
+        <v>0.1828965587397814</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.110548782618064</v>
       </c>
       <c r="E36">
-        <v>-19.39223650654029</v>
+        <v>-20.35295226726755</v>
       </c>
       <c r="F36">
-        <v>-0.9586202112037001</v>
+        <v>-0.7867255629948602</v>
       </c>
       <c r="G36">
-        <v>0.9961055860974343</v>
+        <v>-0.618109797760118</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-1.061173547257687</v>
       </c>
       <c r="E37">
-        <v>-17.40017437598812</v>
+        <v>-21.08019349358136</v>
       </c>
       <c r="F37">
-        <v>-1.029619331098766</v>
+        <v>-0.8832389770406133</v>
       </c>
       <c r="G37">
-        <v>1.073962996090014</v>
+        <v>0.2015812777634279</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8162670610648661</v>
       </c>
       <c r="E38">
-        <v>-17.76535504844067</v>
+        <v>-20.56161529259299</v>
       </c>
       <c r="F38">
-        <v>-1.342767085464523</v>
+        <v>-0.7489589280293757</v>
       </c>
       <c r="G38">
-        <v>0.739925640632012</v>
+        <v>-0.04895418755753696</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.4021402587775039</v>
       </c>
       <c r="E39">
-        <v>-17.90717779741289</v>
+        <v>-19.2500197803294</v>
       </c>
       <c r="F39">
-        <v>-1.408517012102865</v>
+        <v>-0.5609271083951655</v>
       </c>
       <c r="G39">
-        <v>1.048322820888359</v>
+        <v>1.460009021969966</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.1574249095117708</v>
       </c>
       <c r="E40">
-        <v>-16.75393396424952</v>
+        <v>-19.51322374660322</v>
       </c>
       <c r="F40">
-        <v>-1.699907022749358</v>
+        <v>-0.3014028444732301</v>
       </c>
       <c r="G40">
-        <v>1.63414702788117</v>
+        <v>-0.3700009623194389</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.8289079658395556</v>
       </c>
       <c r="E41">
-        <v>-16.73239654186904</v>
+        <v>-18.93375568410771</v>
       </c>
       <c r="F41">
-        <v>-1.993771573888724</v>
+        <v>-1.097013936330292</v>
       </c>
       <c r="G41">
-        <v>1.837911105823312</v>
+        <v>0.3640562317397792</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.569843831664768</v>
       </c>
       <c r="E42">
-        <v>-14.55927696354219</v>
+        <v>-16.31502067800408</v>
       </c>
       <c r="F42">
-        <v>-1.61651461221302</v>
+        <v>-0.8096243668261991</v>
       </c>
       <c r="G42">
-        <v>1.814604865226843</v>
+        <v>0.8287939250882078</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.346668516467358</v>
       </c>
       <c r="E43">
-        <v>-15.98702330562852</v>
+        <v>-16.0092082997921</v>
       </c>
       <c r="F43">
-        <v>-1.296711333737629</v>
+        <v>-1.518195773423666</v>
       </c>
       <c r="G43">
-        <v>1.890694443901451</v>
+        <v>1.803193414752975</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>3.123768414503523</v>
       </c>
       <c r="E44">
-        <v>-14.98753927892159</v>
+        <v>-15.5853114333561</v>
       </c>
       <c r="F44">
-        <v>-1.638023714103561</v>
+        <v>-1.22596323123016</v>
       </c>
       <c r="G44">
-        <v>1.802627311465759</v>
+        <v>1.576649472955108</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>3.862802947163855</v>
       </c>
       <c r="E45">
-        <v>-13.70514336705946</v>
+        <v>-15.47377964702118</v>
       </c>
       <c r="F45">
-        <v>-1.517599508146503</v>
+        <v>-1.222323083183522</v>
       </c>
       <c r="G45">
-        <v>2.132936992646542</v>
+        <v>0.8394902977255929</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.540564738345513</v>
       </c>
       <c r="E46">
-        <v>-12.59677218283809</v>
+        <v>-16.09392699152759</v>
       </c>
       <c r="F46">
-        <v>-1.566075954365147</v>
+        <v>-1.057681808067395</v>
       </c>
       <c r="G46">
-        <v>1.977857797404923</v>
+        <v>1.721571914482244</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.137954953795377</v>
       </c>
       <c r="E47">
-        <v>-13.65679737855357</v>
+        <v>-14.91166922539708</v>
       </c>
       <c r="F47">
-        <v>-1.526175275678608</v>
+        <v>-1.40099361715157</v>
       </c>
       <c r="G47">
-        <v>2.95243605652881</v>
+        <v>1.617094407808384</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.637671223768682</v>
       </c>
       <c r="E48">
-        <v>-11.49902479863872</v>
+        <v>-13.84139609300224</v>
       </c>
       <c r="F48">
-        <v>-1.892157834942298</v>
+        <v>-1.367005704500324</v>
       </c>
       <c r="G48">
-        <v>2.8920682586202</v>
+        <v>1.696189961832651</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.037108470850029</v>
       </c>
       <c r="E49">
-        <v>-12.50996133611105</v>
+        <v>-12.73575105013349</v>
       </c>
       <c r="F49">
-        <v>-1.720659905065276</v>
+        <v>-1.267014472264266</v>
       </c>
       <c r="G49">
-        <v>3.00431230512919</v>
+        <v>0.4306908923542297</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>6.335762548840914</v>
       </c>
       <c r="E50">
-        <v>-11.63520506899738</v>
+        <v>-12.03940760197402</v>
       </c>
       <c r="F50">
-        <v>-1.780462224138185</v>
+        <v>-1.319904706869239</v>
       </c>
       <c r="G50">
-        <v>2.49910981365425</v>
+        <v>1.715311672867482</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>6.534326597341553</v>
       </c>
       <c r="E51">
-        <v>-10.00051199323453</v>
+        <v>-12.62969418887385</v>
       </c>
       <c r="F51">
-        <v>-1.689342912440419</v>
+        <v>-1.290838160350221</v>
       </c>
       <c r="G51">
-        <v>2.807384503725643</v>
+        <v>0.507614728504735</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>6.642903144774701</v>
       </c>
       <c r="E52">
-        <v>-9.895917829079366</v>
+        <v>-10.82368441292682</v>
       </c>
       <c r="F52">
-        <v>-1.630075094113971</v>
+        <v>-1.398424846156727</v>
       </c>
       <c r="G52">
-        <v>2.321154748736266</v>
+        <v>1.819372050803393</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>6.668683533625179</v>
       </c>
       <c r="E53">
-        <v>-8.764582753165103</v>
+        <v>-10.61822301872481</v>
       </c>
       <c r="F53">
-        <v>-2.069124301345333</v>
+        <v>-1.411521302224454</v>
       </c>
       <c r="G53">
-        <v>2.667437812144033</v>
+        <v>1.696729580755553</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>6.620817972195741</v>
       </c>
       <c r="E54">
-        <v>-7.558233505313781</v>
+        <v>-9.710010385642475</v>
       </c>
       <c r="F54">
-        <v>-1.767366559923416</v>
+        <v>-0.5753491263141148</v>
       </c>
       <c r="G54">
-        <v>2.18500194234266</v>
+        <v>1.024218738816925</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>6.513718344110374</v>
       </c>
       <c r="E55">
-        <v>-9.527010222518507</v>
+        <v>-9.712763697839138</v>
       </c>
       <c r="F55">
-        <v>-1.643050396679166</v>
+        <v>-0.7117085811923244</v>
       </c>
       <c r="G55">
-        <v>2.767724168165175</v>
+        <v>0.7258160955436382</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>6.35525268735465</v>
       </c>
       <c r="E56">
-        <v>-7.349484438982201</v>
+        <v>-9.158636975890555</v>
       </c>
       <c r="F56">
-        <v>-1.776354090993535</v>
+        <v>-1.199112289286842</v>
       </c>
       <c r="G56">
-        <v>1.582254226553094</v>
+        <v>0.7754808997237845</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>6.157974517028896</v>
       </c>
       <c r="E57">
-        <v>-7.205225370993854</v>
+        <v>-8.232428187101737</v>
       </c>
       <c r="F57">
-        <v>-2.046505813461027</v>
+        <v>-1.095297990970913</v>
       </c>
       <c r="G57">
-        <v>1.064431935482452</v>
+        <v>0.5601299123941939</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>5.936157231963906</v>
       </c>
       <c r="E58">
-        <v>-7.410886018052203</v>
+        <v>-7.025137016656819</v>
       </c>
       <c r="F58">
-        <v>-1.615107489507152</v>
+        <v>-0.9561654670347689</v>
       </c>
       <c r="G58">
-        <v>1.682222770202466</v>
+        <v>0.434759552821994</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>5.696002618553655</v>
       </c>
       <c r="E59">
-        <v>-6.23039435678468</v>
+        <v>-5.479387698878619</v>
       </c>
       <c r="F59">
-        <v>-1.881904130992786</v>
+        <v>-1.397628242081261</v>
       </c>
       <c r="G59">
-        <v>1.84641258676816</v>
+        <v>-0.3987199448726164</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>5.45244761743165</v>
       </c>
       <c r="E60">
-        <v>-5.835321227407502</v>
+        <v>-9.050030583764597</v>
       </c>
       <c r="F60">
-        <v>-1.615029096064338</v>
+        <v>-1.536520834571216</v>
       </c>
       <c r="G60">
-        <v>1.308157608629136</v>
+        <v>-0.4494275708976332</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>5.217857552472783</v>
       </c>
       <c r="E61">
-        <v>-5.446175870506365</v>
+        <v>-6.307795034523781</v>
       </c>
       <c r="F61">
-        <v>-2.068436972978033</v>
+        <v>-1.613240300232849</v>
       </c>
       <c r="G61">
-        <v>1.00257770262671</v>
+        <v>0.1481159673041983</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>4.99553847832149</v>
       </c>
       <c r="E62">
-        <v>-4.582242656271029</v>
+        <v>-4.913708839736469</v>
       </c>
       <c r="F62">
-        <v>-1.787199309102464</v>
+        <v>-1.67795923432024</v>
       </c>
       <c r="G62">
-        <v>0.5862137006981115</v>
+        <v>-1.537183450372585</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>4.799316766450771</v>
       </c>
       <c r="E63">
-        <v>-5.495658505988179</v>
+        <v>-6.742827418544642</v>
       </c>
       <c r="F63">
-        <v>-1.768089521673814</v>
+        <v>-1.28026454780579</v>
       </c>
       <c r="G63">
-        <v>1.145801834292199</v>
+        <v>-1.052357366691859</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>4.634544474779754</v>
       </c>
       <c r="E64">
-        <v>-4.583868378439783</v>
+        <v>-5.561235338093254</v>
       </c>
       <c r="F64">
-        <v>-1.877482424076879</v>
+        <v>-1.710281880201401</v>
       </c>
       <c r="G64">
-        <v>0.03796087503048879</v>
+        <v>-1.823539018428464</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>4.497455233662135</v>
       </c>
       <c r="E65">
-        <v>-3.727280349044889</v>
+        <v>-5.661341784506814</v>
       </c>
       <c r="F65">
-        <v>-1.909558011835232</v>
+        <v>-1.08963861788209</v>
       </c>
       <c r="G65">
-        <v>0.6915022910290923</v>
+        <v>-2.086161285513308</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>4.394452677037151</v>
       </c>
       <c r="E66">
-        <v>-3.686614652456009</v>
+        <v>-5.294304437711125</v>
       </c>
       <c r="F66">
-        <v>-2.049988382769079</v>
+        <v>-1.843900731992943</v>
       </c>
       <c r="G66">
-        <v>-0.3370378603849157</v>
+        <v>-1.272316633412115</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>4.321711538851104</v>
       </c>
       <c r="E67">
-        <v>-2.94033119293995</v>
+        <v>-4.456337493435771</v>
       </c>
       <c r="F67">
-        <v>-2.514410142471696</v>
+        <v>-1.459586776758041</v>
       </c>
       <c r="G67">
-        <v>-0.413498220159923</v>
+        <v>-2.027766572746104</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>4.269278788308286</v>
       </c>
       <c r="E68">
-        <v>-3.292832138171018</v>
+        <v>-4.527801341750816</v>
       </c>
       <c r="F68">
-        <v>-2.435478239646194</v>
+        <v>-2.194826999118551</v>
       </c>
       <c r="G68">
-        <v>-0.04882838682704465</v>
+        <v>-2.037598892997739</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>4.237111081016522</v>
       </c>
       <c r="E69">
-        <v>-3.142246791993955</v>
+        <v>-3.798703441093866</v>
       </c>
       <c r="F69">
-        <v>-2.284418826460876</v>
+        <v>-2.522038853866368</v>
       </c>
       <c r="G69">
-        <v>-0.7568084136734237</v>
+        <v>-2.081069666473909</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>4.216864820587226</v>
       </c>
       <c r="E70">
-        <v>-3.108151911190205</v>
+        <v>-4.134775082625106</v>
       </c>
       <c r="F70">
-        <v>-2.575396281716396</v>
+        <v>-2.072678929272537</v>
       </c>
       <c r="G70">
-        <v>-0.1479262569995884</v>
+        <v>-2.876855292658377</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>4.19881283130714</v>
       </c>
       <c r="E71">
-        <v>-1.776024297775839</v>
+        <v>-3.125301242257253</v>
       </c>
       <c r="F71">
-        <v>-2.416157819330791</v>
+        <v>-1.415079097563488</v>
       </c>
       <c r="G71">
-        <v>-0.01608378089811334</v>
+        <v>-2.795650921125595</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>4.182743075408092</v>
       </c>
       <c r="E72">
-        <v>-4.248584691385878</v>
+        <v>-5.420236771390429</v>
       </c>
       <c r="F72">
-        <v>-2.372544142125504</v>
+        <v>-1.67514974002625</v>
       </c>
       <c r="G72">
-        <v>-0.7909401381833095</v>
+        <v>-2.395270233060598</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>4.16257660627269</v>
       </c>
       <c r="E73">
-        <v>-3.882421340073668</v>
+        <v>-4.781558911244633</v>
       </c>
       <c r="F73">
-        <v>-2.486481488652922</v>
+        <v>-2.453292555636015</v>
       </c>
       <c r="G73">
-        <v>-0.2847544146832058</v>
+        <v>-0.9830775801915307</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>4.134045044429707</v>
       </c>
       <c r="E74">
-        <v>-3.789972543207078</v>
+        <v>-4.081570041508988</v>
       </c>
       <c r="F74">
-        <v>-2.256714267029136</v>
+        <v>-2.402473808368436</v>
       </c>
       <c r="G74">
-        <v>-0.2428230448827969</v>
+        <v>-1.291964721187689</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>4.101028314234488</v>
       </c>
       <c r="E75">
-        <v>-3.857596245563619</v>
+        <v>-4.47212375382651</v>
       </c>
       <c r="F75">
-        <v>-2.548351335798437</v>
+        <v>-2.391197822250507</v>
       </c>
       <c r="G75">
-        <v>0.7077272747170604</v>
+        <v>-1.864238865288264</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>4.062085862520236</v>
       </c>
       <c r="E76">
-        <v>-4.264633603269061</v>
+        <v>-3.928163456025146</v>
       </c>
       <c r="F76">
-        <v>-2.906663215460696</v>
+        <v>-2.662629970950632</v>
       </c>
       <c r="G76">
-        <v>-0.5817103495558312</v>
+        <v>-1.416368401462422</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>4.019101607450387</v>
       </c>
       <c r="E77">
-        <v>-4.659249356771464</v>
+        <v>-7.229787814011458</v>
       </c>
       <c r="F77">
-        <v>-3.075856061377797</v>
+        <v>-3.159779805248764</v>
       </c>
       <c r="G77">
-        <v>0.3505889324860241</v>
+        <v>-1.333111491695291</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>3.977118356600222</v>
       </c>
       <c r="E78">
-        <v>-5.059774768853877</v>
+        <v>-6.336043655383628</v>
       </c>
       <c r="F78">
-        <v>-2.879647568102173</v>
+        <v>-2.56179620716756</v>
       </c>
       <c r="G78">
-        <v>0.6319654400508393</v>
+        <v>-1.496473671876167</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>3.93359478016218</v>
       </c>
       <c r="E79">
-        <v>-5.900662578864178</v>
+        <v>-7.702678240736443</v>
       </c>
       <c r="F79">
-        <v>-3.141581440574449</v>
+        <v>-2.369653878829827</v>
       </c>
       <c r="G79">
-        <v>0.6763631662780052</v>
+        <v>-1.24890114481285</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>3.888187993408928</v>
       </c>
       <c r="E80">
-        <v>-5.550050007294308</v>
+        <v>-7.253181910735083</v>
       </c>
       <c r="F80">
-        <v>-3.006184087039869</v>
+        <v>-2.947513325843541</v>
       </c>
       <c r="G80">
-        <v>1.021570302385508</v>
+        <v>-0.2122038091900777</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.839053104596873</v>
       </c>
       <c r="E81">
-        <v>-6.835656607227876</v>
+        <v>-7.848187167550907</v>
       </c>
       <c r="F81">
-        <v>-3.518786931807901</v>
+        <v>-2.52824381364306</v>
       </c>
       <c r="G81">
-        <v>1.40334903506534</v>
+        <v>-0.2493348879585434</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.777784129453809</v>
       </c>
       <c r="E82">
-        <v>-7.47080225764769</v>
+        <v>-8.260577181533415</v>
       </c>
       <c r="F82">
-        <v>-3.216281681193897</v>
+        <v>-2.737858377492879</v>
       </c>
       <c r="G82">
-        <v>0.7672078464211459</v>
+        <v>-0.3028697198740977</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.69971136083658</v>
       </c>
       <c r="E83">
-        <v>-7.416098291635032</v>
+        <v>-9.605923410576171</v>
       </c>
       <c r="F83">
-        <v>-3.639759100011701</v>
+        <v>-3.55347880173856</v>
       </c>
       <c r="G83">
-        <v>1.577251992243256</v>
+        <v>0.2746615705428394</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.596103234570462</v>
       </c>
       <c r="E84">
-        <v>-9.774604538887884</v>
+        <v>-9.767734843818248</v>
       </c>
       <c r="F84">
-        <v>-3.664907558095922</v>
+        <v>-3.392283670694429</v>
       </c>
       <c r="G84">
-        <v>1.002468454623914</v>
+        <v>0.3739315890834252</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.454452449929093</v>
       </c>
       <c r="E85">
-        <v>-11.14445886926015</v>
+        <v>-11.90857998789243</v>
       </c>
       <c r="F85">
-        <v>-3.779522730755148</v>
+        <v>-3.448386452748871</v>
       </c>
       <c r="G85">
-        <v>1.109028294441974</v>
+        <v>-0.3699546146818891</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.267968616562651</v>
       </c>
       <c r="E86">
-        <v>-11.58459937196167</v>
+        <v>-12.25598639986486</v>
       </c>
       <c r="F86">
-        <v>-3.755871666613975</v>
+        <v>-2.970282265789814</v>
       </c>
       <c r="G86">
-        <v>1.818312676230826</v>
+        <v>0.7441565178312006</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.026950805768351</v>
       </c>
       <c r="E87">
-        <v>-13.49076087906233</v>
+        <v>-13.25327411667808</v>
       </c>
       <c r="F87">
-        <v>-4.004067682122773</v>
+        <v>-3.359857292075807</v>
       </c>
       <c r="G87">
-        <v>1.795648681468976</v>
+        <v>0.7130042843066587</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.723624232248756</v>
       </c>
       <c r="E88">
-        <v>-14.64889093567998</v>
+        <v>-14.94555579639647</v>
       </c>
       <c r="F88">
-        <v>-3.843552752769322</v>
+        <v>-3.584214574292451</v>
       </c>
       <c r="G88">
-        <v>1.360960809980512</v>
+        <v>1.127911646197977</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.358131417695769</v>
       </c>
       <c r="E89">
-        <v>-15.77402653067774</v>
+        <v>-16.5059049143754</v>
       </c>
       <c r="F89">
-        <v>-4.186035491806765</v>
+        <v>-3.775740841029078</v>
       </c>
       <c r="G89">
-        <v>2.205411455592267</v>
+        <v>0.7721074538192673</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.92876429358573</v>
       </c>
       <c r="E90">
-        <v>-17.30739952899298</v>
+        <v>-17.50539799803035</v>
       </c>
       <c r="F90">
-        <v>-4.410703972235793</v>
+        <v>-3.398245531613101</v>
       </c>
       <c r="G90">
-        <v>1.347672280185877</v>
+        <v>0.5545119166140506</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.440629039351644</v>
       </c>
       <c r="E91">
-        <v>-18.39723114062694</v>
+        <v>-19.56536912480154</v>
       </c>
       <c r="F91">
-        <v>-3.980730191752857</v>
+        <v>-3.190603473480962</v>
       </c>
       <c r="G91">
-        <v>2.423679033541955</v>
+        <v>-0.2042849842601411</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.9017586192047312</v>
       </c>
       <c r="E92">
-        <v>-20.70688873875906</v>
+        <v>-21.61980645633536</v>
       </c>
       <c r="F92">
-        <v>-4.203317682608998</v>
+        <v>-3.421002593765008</v>
       </c>
       <c r="G92">
-        <v>1.358954619383713</v>
+        <v>-0.4684830710216781</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.317737375651689</v>
       </c>
       <c r="E93">
-        <v>-22.8059722955345</v>
+        <v>-23.2094412157219</v>
       </c>
       <c r="F93">
-        <v>-4.410829876856071</v>
+        <v>-3.537923642237114</v>
       </c>
       <c r="G93">
-        <v>0.5498870844956888</v>
+        <v>0.3502148408400864</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.2981030129677225</v>
       </c>
       <c r="E94">
-        <v>-24.8008284945494</v>
+        <v>-25.53123512419456</v>
       </c>
       <c r="F94">
-        <v>-4.330354652615973</v>
+        <v>-3.934040165806828</v>
       </c>
       <c r="G94">
-        <v>0.6813091213136764</v>
+        <v>0.07177809771414397</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.9349920309877681</v>
       </c>
       <c r="E95">
-        <v>-26.36590986786634</v>
+        <v>-28.01885722235411</v>
       </c>
       <c r="F95">
-        <v>-4.478839751835745</v>
+        <v>-3.782148515162946</v>
       </c>
       <c r="G95">
-        <v>0.1468380967260396</v>
+        <v>-0.556205906721286</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.585272531295318</v>
       </c>
       <c r="E96">
-        <v>-29.03660005625997</v>
+        <v>-29.92939323534619</v>
       </c>
       <c r="F96">
-        <v>-4.054038354872633</v>
+        <v>-3.778361874319131</v>
       </c>
       <c r="G96">
-        <v>0.2265527227661505</v>
+        <v>-0.5952405491748326</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.229168418214025</v>
       </c>
       <c r="E97">
-        <v>-32.13393589481226</v>
+        <v>-31.81885599454358</v>
       </c>
       <c r="F97">
-        <v>-4.773803394880426</v>
+        <v>-2.753021569780254</v>
       </c>
       <c r="G97">
-        <v>0.2244008681656242</v>
+        <v>-0.903975405076185</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.862013080967361</v>
       </c>
       <c r="E98">
-        <v>-33.57694093006743</v>
+        <v>-33.89689120413136</v>
       </c>
       <c r="F98">
-        <v>-4.357051183232536</v>
+        <v>-4.178173975642523</v>
       </c>
       <c r="G98">
-        <v>-0.5789957022136289</v>
+        <v>-0.804043277427745</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.462980061581177</v>
       </c>
       <c r="E99">
-        <v>-36.53478165528744</v>
+        <v>-36.65383297271209</v>
       </c>
       <c r="F99">
-        <v>-4.642869716468512</v>
+        <v>-3.546859702864981</v>
       </c>
       <c r="G99">
-        <v>0.2024188457848635</v>
+        <v>-1.879950714417645</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.030144040972401</v>
       </c>
       <c r="E100">
-        <v>-39.90006956511058</v>
+        <v>-38.3654263298362</v>
       </c>
       <c r="F100">
-        <v>-4.725014958596441</v>
+        <v>-4.03856871549062</v>
       </c>
       <c r="G100">
-        <v>-1.690534540842705</v>
+        <v>-1.607257767802338</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.529002373435555</v>
       </c>
       <c r="E101">
-        <v>-40.18309013364197</v>
+        <v>-41.62160292268153</v>
       </c>
       <c r="F101">
-        <v>-4.648949563477884</v>
+        <v>-3.863124982325281</v>
       </c>
       <c r="G101">
-        <v>-1.122825639040785</v>
+        <v>-2.449182467167629</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.986926760918496</v>
       </c>
       <c r="E102">
-        <v>-43.59364240540878</v>
+        <v>-45.32326361755742</v>
       </c>
       <c r="F102">
-        <v>-4.658223745318698</v>
+        <v>-3.728662807133768</v>
       </c>
       <c r="G102">
-        <v>-1.782915314116067</v>
+        <v>-3.215739286785873</v>
       </c>
     </row>
   </sheetData>
